--- a/переводы-13.5/06 The Wolf of Wall Street.xlsx
+++ b/переводы-13.5/06 The Wolf of Wall Street.xlsx
@@ -3588,12 +3588,12 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Darauf kannst du dich verlassen.</t>
+          <t>Darauf kannst du einen lassen.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Уж будь уверен.</t>
+          <t>Отвечаю.</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -3603,49 +3603,49 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Когда твёрдо обещаешь или уверяешь: можешь на это рассчитывать.</t>
+          <t>Когда грубовато и уверенно обещаешь: сто процентов так и будет.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Ich bin um acht da, darauf kannst du dich verlassen.</t>
+          <t>Morgen gewinnen wir, darauf kannst du einen lassen!</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Буду в восемь, можешь на меня рассчитывать.</t>
+          <t>Завтра мы выиграем — отвечаю!</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Когда твёрдо обещаешь или уверяешь: можешь на это рассчитывать.</t>
+          <t>Когда грубовато и уверенно обещаешь: сто процентов так и будет.</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>I'll be there at eight, you can count on it. — Буду в восемь, можешь на меня рассчитывать. — Ich bin um acht da, darauf kannst du dich verlassen.</t>
+          <t>We'll win tomorrow, you can bet on it! — Завтра мы выиграем — отвечаю! — Morgen gewinnen wir, darauf kannst du einen lassen!</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Ich bin um acht da, darauf kannst du dich verlassen. — Буду в восемь, можешь на меня рассчитывать.</t>
+          <t>Morgen gewinnen wir, darauf kannst du einen lassen! — Завтра мы выиграем — отвечаю!</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Отсюда ты можешь уйти. / На это ты можешь не рассчитывать. / Это ты можешь оставить.</t>
+          <t>На это можешь не рассчитывать. / Можешь это отпустить. / Это можешь оставить себе.</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>verlassen</t>
+          <t>lassen</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr"/>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>общение</t>
+          <t>ссоры</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -8155,37 +8155,37 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Darauf kannst du dich verlassen.</t>
+          <t>Darauf kannst du einen lassen.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>verlassen</t>
+          <t>einen lassen</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>sich auf etwas verlassen</t>
+          <t>Darauf kannst du einen lassen.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>полагаться на что-то</t>
+          <t>(груб.) отвечаю, зуб даю</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Auf ihn kann man sich verlassen.</t>
+          <t>Der kommt zu spät, darauf kannst du einen lassen.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>На него можно положиться.</t>
+          <t>Он опоздает, зуб даю.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>sich verlassen auf + Akk. Без sich: verlassen — «покидать».</t>
+          <t>Грубая идиома, дословно «на это можно пукнуть». Вежливо то же самое — Darauf kannst du dich verlassen.</t>
         </is>
       </c>
     </row>
@@ -13129,12 +13129,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Wir kassieren die Provisionen. Darauf kannst du dich verlassen.</t>
+          <t>Wir kassieren die Provisionen. Darauf kannst du einen lassen.</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Мы получаем комиссионные. Уж будь уверен.</t>
+          <t>Мы получаем комиссионные. Отвечаю.</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Так что душишь змея — и кровь не застаивается.</t>
+          <t>Так что душишь удава — и кровь не застаивается.</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
